--- a/artfynd/A 32913-2021 artfynd.xlsx
+++ b/artfynd/A 32913-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32913-2021 artfynd.xlsx
+++ b/artfynd/A 32913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56077745</v>
+        <v>56077748</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533544.5036368211</v>
+        <v>533496</v>
       </c>
       <c r="R2" t="n">
-        <v>7040407.390842446</v>
+        <v>7040329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-05-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-05-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +769,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>56077745</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>533545</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7040407</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-05-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-05-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
